--- a/isolated_excel/Table 2 - Current Update.xlsx
+++ b/isolated_excel/Table 2 - Current Update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Table 2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 2'!$A$1:$C$18</definedName>

--- a/isolated_excel/Table 2 - Current Update.xlsx
+++ b/isolated_excel/Table 2 - Current Update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Table 2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 2'!$A$1:$C$18</definedName>
@@ -442,7 +442,7 @@
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.495221238938055</v>
+        <v>3.520614035087721</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1.327549492803307</v>
+        <v>1.307550607795648</v>
       </c>
     </row>
     <row r="3">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.422856966733567</v>
+        <v>3.448521353622169</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.224931146566699</v>
+        <v>1.205625872082727</v>
       </c>
     </row>
     <row r="4">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.57522123893806</v>
+        <v>95.6140350877193</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>70.79646017699115</v>
+        <v>70.17543859649122</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.424778761061947</v>
+        <v>4.385964912280701</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>29.20353982300885</v>
+        <v>29.82456140350877</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.697222222222224</v>
+        <v>3.721926605504589</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>3.616317163875842</v>
@@ -537,7 +537,7 @@
         <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-4.220978194645264</v>
+        <v>-4.124841288863633</v>
       </c>
     </row>
     <row r="8">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.495221238938055</v>
+        <v>3.520614035087721</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.327549492803307</v>
+        <v>1.307550607795648</v>
       </c>
     </row>
     <row r="11">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4.010102220229272</v>
+        <v>4.001514378174758</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4.543739913577447</v>
+        <v>4.528627069815164</v>
       </c>
     </row>
     <row r="12">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.649552522801262</v>
+        <v>2.626664430542024</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.4507028811013239</v>
+        <v>-0.438794641537164</v>
       </c>
     </row>
     <row r="13">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.518273050774795</v>
+        <v>8.443105350916397</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.5164587239200782</v>
+        <v>0.5239364253231313</v>
       </c>
     </row>
     <row r="14">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8716040257792284</v>
+        <v>0.8798204135639283</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.2921711009110292</v>
+        <v>0.2887300251572749</v>
       </c>
     </row>
     <row r="15">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.35776078315886</v>
+        <v>14.52592048115421</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.4733519514863244</v>
+        <v>0.4680407905555371</v>
       </c>
     </row>
     <row r="16">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>92.0046082949309</v>
+        <v>93.47695852534564</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.07696630589219</v>
+        <v>2.062862778510679</v>
       </c>
     </row>
     <row r="17">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.525269540287813</v>
+        <v>3.553834897000299</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02263441138176098</v>
+        <v>-0.02540694158567561</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
@@ -734,7 +734,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to May 2026; 113 monthly observations</t>
+          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Table 2 - Current Update.xlsx
+++ b/isolated_excel/Table 2 - Current Update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Table 2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 2'!$A$1:$C$18</definedName>
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.520614035087721</v>
+        <v>3.519478260869565</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1.307550607795648</v>
+        <v>1.295628487903424</v>
       </c>
     </row>
     <row r="3">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.448521353622169</v>
+        <v>3.448012329545969</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1.205625872082727</v>
+        <v>1.194520884974981</v>
       </c>
     </row>
     <row r="4">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>95.6140350877193</v>
+        <v>95.65217391304348</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>70.17543859649122</v>
+        <v>69.56521739130434</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4.385964912280701</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>29.82456140350877</v>
+        <v>30.43478260869566</v>
       </c>
     </row>
     <row r="6">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.721926605504589</v>
+        <v>3.718909090909091</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.616317163875842</v>
+        <v>3.616317163875843</v>
       </c>
     </row>
     <row r="7">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.8680000000000002</v>
+        <v>-0.868</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>-4.124841288863633</v>
+        <v>-4.008802771462106</v>
       </c>
     </row>
     <row r="8">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.520614035087721</v>
+        <v>3.519478260869565</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.307550607795648</v>
+        <v>1.295628487903424</v>
       </c>
     </row>
     <row r="11">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4.001514378174758</v>
+        <v>3.983943837120484</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4.528627069815164</v>
+        <v>4.510533237481415</v>
       </c>
     </row>
     <row r="12">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.626664430542024</v>
+        <v>2.638684739182457</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.438794641537164</v>
+        <v>-0.4323133842228436</v>
       </c>
     </row>
     <row r="13">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.443105350916397</v>
+        <v>8.543303212889626</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.5239364253231313</v>
+        <v>0.5443369456982401</v>
       </c>
     </row>
     <row r="14">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8798204135639283</v>
+        <v>0.8834156315349503</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.2887300251572749</v>
+        <v>0.287245081609658</v>
       </c>
     </row>
     <row r="15">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.52592048115421</v>
+        <v>14.58478488287688</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.4680407905555371</v>
+        <v>0.4658018365243973</v>
       </c>
     </row>
     <row r="16">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>93.47695852534564</v>
+        <v>94.25806451612902</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.062862778510679</v>
+        <v>2.061929277735463</v>
       </c>
     </row>
     <row r="17">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.553834897000299</v>
+        <v>3.552270603645034</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02540694158567561</v>
+        <v>-0.02530998899887835</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
@@ -734,7 +734,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
+          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Table 2 - Current Update.xlsx
+++ b/isolated_excel/Table 2 - Current Update.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Table 2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 2'!$A$1:$C$18</definedName>
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.519478260869565</v>
+        <v>3.519478260869567</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1.295628487903424</v>
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3.718909090909091</v>
+        <v>3.718909090909092</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.616317163875843</v>
+        <v>3.616317163875842</v>
       </c>
     </row>
     <row r="7">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.868</v>
+        <v>-0.8680000000000002</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-4.008802771462106</v>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3.519478260869565</v>
+        <v>3.519478260869567</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1.295628487903424</v>
@@ -589,7 +589,7 @@
         <v>3.983943837120484</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4.510533237481415</v>
+        <v>4.510533237481414</v>
       </c>
     </row>
     <row r="12">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>2.638684739182457</v>
+        <v>2.638684739182456</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.4323133842228436</v>
+        <v>-0.4323133842228444</v>
       </c>
     </row>
     <row r="13">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>8.543303212889626</v>
+        <v>8.54330321288962</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.5443369456982401</v>
+        <v>0.5443369456982423</v>
       </c>
     </row>
     <row r="14">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.8834156315349503</v>
+        <v>0.8834156315349508</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.287245081609658</v>
+        <v>0.2872450816096581</v>
       </c>
     </row>
     <row r="15">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>14.58478488287688</v>
+        <v>14.58478488287689</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0.4658018365243973</v>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>94.25806451612902</v>
+        <v>94.25806451612905</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>2.061929277735463</v>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.552270603645034</v>
+        <v>3.552270603645037</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.02530998899887835</v>
+        <v>-0.02530998899887851</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>1</v>
